--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260701.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260701.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.39%</t>
+          <t>11.40%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.99%</t>
+          <t>10.01%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>9.05%</t>
+          <t>8.72%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.66%</t>
+          <t>7.62%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>5.23%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>4.40%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>4.05%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.32%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1012,29 +1012,29 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>5,210</t>
+          <t>34,421</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1056,117 +1056,117 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>34,421</t>
+          <t>5,210</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>81,526</t>
+          <t>53,001</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>53,001</t>
+          <t>81,526</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>23,566</t>
+          <t>32,234</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>32,234</t>
+          <t>23,566</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1408,46 +1408,46 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>6,223</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>202609ESU6</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6,223</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7,228</t>
+          <t>46,038</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,61 +1525,61 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>46,038</t>
+          <t>7,228</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MYRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>MYR集團公司</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>3,866</t>
+          <t>17,075</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>17,075</t>
+          <t>3,866</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>97,979,295</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
